--- a/data/EVALUACIONES/AEROBICO/AERÓBICO_5MIN.xlsx
+++ b/data/EVALUACIONES/AEROBICO/AERÓBICO_5MIN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\AEROBICO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9A8A5C-6FE7-4241-8699-1574F2CE792B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC753C1-2DA3-4CB5-A872-FA19813BE635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
   <si>
     <t>Fecha</t>
   </si>
@@ -117,7 +117,13 @@
     <t>rodrigo_cueva</t>
   </si>
   <si>
-    <t>Jaime_Munoz_Garcia</t>
+    <t xml:space="preserve">Presley_Osarenkhoe </t>
+  </si>
+  <si>
+    <t>Jaime_Muñoz_Garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan_Manuel_Ruiz </t>
   </si>
 </sst>
 </file>
@@ -221,9 +227,7 @@
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre"/>
     <tableColumn id="3" xr3:uid="{7181ECEA-9A38-48C9-BBA4-EA4A27B75232}" name="Distancia"/>
     <tableColumn id="4" xr3:uid="{E14E909A-C1B7-46F7-BDF3-44821CD907E1}" name="Tiempo "/>
-    <tableColumn id="5" xr3:uid="{CAAE935B-BE10-4E7F-BA65-ADAE989D0116}" name="VAM_(km/h)" dataDxfId="0">
-      <calculatedColumnFormula>(C2/D2)*60</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="5" xr3:uid="{CAAE935B-BE10-4E7F-BA65-ADAE989D0116}" name="VAM_(km/h)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -555,17 +559,16 @@
         <v>46569</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C2">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
       <c r="E2" s="1">
-        <f>(C2/D2)*60</f>
-        <v>16.559999999999999</v>
+        <v>16.079999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -573,17 +576,16 @@
         <v>46569</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3:E24" si="0">(C3/D3)*60</f>
-        <v>16.32</v>
+        <v>16.559999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -591,14 +593,16 @@
         <v>46569</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>1.36</v>
       </c>
       <c r="D4">
         <v>5</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -606,17 +610,13 @@
         <v>46569</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1.44</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5" s="1">
-        <f t="shared" si="0"/>
-        <v>17.279999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -624,17 +624,16 @@
         <v>46569</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <f t="shared" si="0"/>
-        <v>16.200000000000003</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -642,17 +641,16 @@
         <v>46569</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="D7">
         <v>5</v>
       </c>
       <c r="E7" s="1">
-        <f t="shared" si="0"/>
-        <v>17.16</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -660,17 +658,16 @@
         <v>46569</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" s="1">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -678,14 +675,16 @@
         <v>46569</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>1.2</v>
       </c>
       <c r="D9">
         <v>5</v>
       </c>
       <c r="E9" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -693,17 +692,13 @@
         <v>46569</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10">
-        <v>1.41</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
       <c r="E10" s="1">
-        <f t="shared" si="0"/>
-        <v>16.919999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -711,17 +706,16 @@
         <v>46569</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="D11">
         <v>5</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" si="0"/>
-        <v>16.32</v>
+        <v>16.920000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -729,14 +723,16 @@
         <v>46569</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>1.36</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
       <c r="E12" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -744,17 +740,13 @@
         <v>46569</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13">
-        <v>1.33</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>5</v>
       </c>
       <c r="E13" s="1">
-        <f t="shared" si="0"/>
-        <v>15.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -762,17 +754,16 @@
         <v>46569</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" s="1">
-        <f t="shared" si="0"/>
-        <v>16.080000000000002</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -780,17 +771,16 @@
         <v>46569</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15" s="1">
-        <f t="shared" si="0"/>
-        <v>16.440000000000001</v>
+        <v>16.079999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -798,14 +788,16 @@
         <v>46569</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="C16">
+        <v>1.37</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.440000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -813,17 +805,16 @@
         <v>46569</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
       <c r="E17" s="1">
-        <f t="shared" si="0"/>
-        <v>16.200000000000003</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -831,14 +822,16 @@
         <v>46569</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>1.35</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -846,17 +839,13 @@
         <v>46569</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19">
-        <v>1.1499999999999999</v>
+        <v>21</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" si="0"/>
-        <v>13.799999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -864,17 +853,16 @@
         <v>46569</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
-        <v>1.31</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="0"/>
-        <v>15.72</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -882,17 +870,16 @@
         <v>46569</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="D21">
         <v>5</v>
       </c>
       <c r="E21" s="1">
-        <f t="shared" si="0"/>
-        <v>16.200000000000003</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -900,17 +887,16 @@
         <v>46569</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="D22">
         <v>5</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -918,17 +904,16 @@
         <v>46569</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
-        <v>0.86</v>
+        <v>1.5</v>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="0"/>
-        <v>10.319999999999999</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -936,17 +921,16 @@
         <v>46569</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
-        <v>1.4</v>
+        <v>0.86</v>
       </c>
       <c r="D24">
         <v>5</v>
       </c>
       <c r="E24" s="1">
-        <f t="shared" si="0"/>
-        <v>16.799999999999997</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -954,17 +938,16 @@
         <v>46569</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C25">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
       <c r="E25" s="1">
-        <f t="shared" ref="E25:E27" si="1">(C25/D25)*60</f>
-        <v>15.96</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -972,14 +955,16 @@
         <v>46569</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+      <c r="C26">
+        <v>1.33</v>
       </c>
       <c r="D26">
         <v>5</v>
       </c>
       <c r="E26" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -987,300 +972,443 @@
         <v>46569</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>5</v>
       </c>
       <c r="E27" s="1">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46600</v>
+        <v>46569</v>
       </c>
       <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28">
+        <v>1.19</v>
+      </c>
+      <c r="D28">
         <v>5</v>
       </c>
       <c r="E28" s="1">
-        <v>18</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46600</v>
+        <v>46569</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
       </c>
       <c r="E29" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>1.38</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
       </c>
       <c r="E30" s="1">
-        <v>12</v>
+        <v>16.559999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>1.44</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
       </c>
       <c r="E31" s="1">
-        <v>9</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>1.34</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
       </c>
       <c r="E32" s="1">
-        <v>9</v>
+        <v>16.079999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>1.51</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
       </c>
       <c r="E33" s="1">
-        <v>9</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C34">
+        <v>1.35</v>
+      </c>
+      <c r="D34">
+        <v>5</v>
       </c>
       <c r="E34" s="1">
-        <v>9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="C35">
+        <v>1.54</v>
+      </c>
+      <c r="D35">
+        <v>5</v>
       </c>
       <c r="E35" s="1">
-        <v>9</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="C36">
+        <v>1.25</v>
+      </c>
+      <c r="D36">
+        <v>5</v>
       </c>
       <c r="E36" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
       </c>
       <c r="E37" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="C38">
+        <v>1.41</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
       </c>
       <c r="E38" s="1">
-        <v>9</v>
+        <v>16.920000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="C39">
+        <v>1.59</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
       </c>
       <c r="E39" s="1">
-        <v>9</v>
+        <v>19.079999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="D40">
+        <v>5</v>
       </c>
       <c r="E40" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="C41">
+        <v>1.35</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
       </c>
       <c r="E41" s="1">
-        <v>9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="C42">
+        <v>1.34</v>
+      </c>
+      <c r="D42">
+        <v>5</v>
       </c>
       <c r="E42" s="1">
-        <v>9</v>
+        <v>16.079999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="C43">
+        <v>1.48</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
       </c>
       <c r="E43" s="1">
-        <v>9</v>
+        <v>17.760000000000002</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="C44">
+        <v>1.3</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
       </c>
       <c r="E44" s="1">
-        <v>9</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="C45">
+        <v>1.24</v>
+      </c>
+      <c r="D45">
+        <v>5</v>
       </c>
       <c r="E45" s="1">
-        <v>9</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
       </c>
       <c r="E46" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="C47">
+        <v>1.33</v>
+      </c>
+      <c r="D47">
+        <v>5</v>
       </c>
       <c r="E47" s="1">
-        <v>9</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="C48">
+        <v>1.39</v>
+      </c>
+      <c r="D48">
+        <v>5</v>
       </c>
       <c r="E48" s="1">
-        <v>9</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="C49">
+        <v>1.42</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
       </c>
       <c r="E49" s="1">
-        <v>9</v>
+        <v>17.04</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="C50">
+        <v>1.5</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
       </c>
       <c r="E50" s="1">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="C51">
+        <v>1.24</v>
+      </c>
+      <c r="D51">
+        <v>5</v>
       </c>
       <c r="E51" s="1">
-        <v>9</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="C52">
+        <v>1.47</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
       </c>
       <c r="E52" s="1">
-        <v>9</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46600</v>
+        <v>46602</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="C53">
+        <v>1.45</v>
+      </c>
+      <c r="D53">
+        <v>5</v>
       </c>
       <c r="E53" s="1">
-        <v>9</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/EVALUACIONES/AEROBICO/AERÓBICO_5MIN.xlsx
+++ b/data/EVALUACIONES/AEROBICO/AERÓBICO_5MIN.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC753C1-2DA3-4CB5-A872-FA19813BE635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="22500" yWindow="1590" windowWidth="17280" windowHeight="9960" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
